--- a/astro-site/public/dl/pizza-shop-checklist-templates/02-pizza-kitchen-station-checklists.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/02-pizza-kitchen-station-checklists.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Check oven temp: 750–840 °F Neapolitan / 570 °F Roman — log reading: ____ °F</t>
+          <t>Check oven temp: 750–840 °F Neapolitan / 570 °F Roman; gas deck or conveyor: your recipe's target — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Watch bake time: 60–90 sec Neapolitan / 3–5 min Roman</t>
+          <t>Watch bake time: 60–90 sec Neapolitan / 3–5 min Roman; deck or conveyor: your recipe's time</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -1116,9 +1116,9 @@
       <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>Check doneness: leopard spotting, not burnt</t>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Check doneness: browned rim and crisp bottom (leopard spotting on Neapolitan), not burnt</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Set up make line inserts: tomato sauce, mozzarella, toppings — all at 41 °F or below (FDA 3-501.16)</t>
+          <t>Set up make line inserts: tomato sauce, mozzarella, toppings — all at 41 °F or below (FDA 3-501.16); don't fill above the cold line and keep the lid closed between orders — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
